--- a/booking_forms/034_researcher_collaboration_lodge_booking_form--booking_forms.xlsx
+++ b/booking_forms/034_researcher_collaboration_lodge_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequestform</t>
+          <t>researchercollaborationlodgerequestform_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Researcher collaboration lodge request to form</t>
+          <t>Researchercollaborationlodgerequestform 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Researcher collaboration lodge request to form</t>
+          <t>Researchercollaborationlodgerequesttoform</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequesttoform</t>
+          <t>researchercollaborationlodgerequesttoform_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Researcher collaboration lodge request to form</t>
+          <t>Researchercollaborationlodgerequesttoform 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequesttoform</t>
+          <t>researchercollaborationlodgerequesttoform_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Researcher collaboration lodge request to form</t>
+          <t>Researchercollaborationlodgerequesttoform 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -987,7 +987,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequestform_choices</t>
+          <t>researchercollaborationlodgerequestform_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,51 +1004,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequestform_choices</t>
+          <t>researchercollaborationlodgerequestform_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bank transfer</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequestform_choices</t>
+          <t>researchercollaborationlodgerequestform_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequestform_choices</t>
+          <t>researchercollaborationlodgerequesttoform_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1060,95 +1060,78 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequesttoform_choices</t>
+          <t>researchercollaborationlodgerequesttoform_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequesttoform_choices</t>
+          <t>researchercollaborationlodgerequesttoform_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequesttoform_choices</t>
+          <t>researchercollaborationlodgerequesttoform_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>researchercollaborationlodgerequesttoform_choices</t>
+          <t>researchercollaborationlodgerequesttoform_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>researchercollaborationlodgerequesttoform_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
